--- a/data/trans_orig/P59A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P59A-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2007</t>
+          <t>Población según si viven actualmente en pareja en 2007 (tasa de respuesta: 98,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10681</t>
+          <t>10308</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26482</t>
+          <t>26901</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>9,29%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6812</t>
+          <t>7260</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>21519</t>
+          <t>22860</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21447</t>
+          <t>21939</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>42224</t>
+          <t>44199</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,97%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88465</t>
+          <t>88046</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104266</t>
+          <t>104639</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,6%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>90,71%</t>
+          <t>91,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98541</t>
+          <t>97200</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113248</t>
+          <t>112800</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>93,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>192783</t>
+          <t>190808</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>213560</t>
+          <t>213068</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,03%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,87%</t>
+          <t>90,66%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>12835</t>
+          <t>13469</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33991</t>
+          <t>33646</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>7,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11829</t>
+          <t>12046</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29261</t>
+          <t>29851</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>28293</t>
+          <t>29408</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>54335</t>
+          <t>56769</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,35%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,75%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>153984</t>
+          <t>154329</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>175140</t>
+          <t>174506</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>92,83%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>167558</t>
+          <t>166968</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184990</t>
+          <t>184773</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>330460</t>
+          <t>328026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>356502</t>
+          <t>355387</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,65%</t>
+          <t>92,36%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11460</t>
+          <t>11515</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26952</t>
+          <t>28075</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6908</t>
+          <t>7074</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>21423</t>
+          <t>20277</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>14,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>22092</t>
+          <t>21213</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41970</t>
+          <t>42315</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,64%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89070</t>
+          <t>87947</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104562</t>
+          <t>104507</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>116894</t>
+          <t>118040</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131409</t>
+          <t>131243</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>85,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212369</t>
+          <t>212024</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>232247</t>
+          <t>233126</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,5%</t>
+          <t>83,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,31%</t>
+          <t>91,66%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13442</t>
+          <t>14176</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30813</t>
+          <t>31667</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15365</t>
+          <t>15366</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34614</t>
+          <t>32476</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>34837</t>
+          <t>33066</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>59372</t>
+          <t>58305</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111439</t>
+          <t>110585</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128810</t>
+          <t>128076</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>77,74%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,03%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>137100</t>
+          <t>139238</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156349</t>
+          <t>156348</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>81,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>254594</t>
+          <t>255661</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>279129</t>
+          <t>280900</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>89,47%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9597</t>
+          <t>9057</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23368</t>
+          <t>23432</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7057</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19650</t>
+          <t>19838</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>24,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>19418</t>
+          <t>18934</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38106</t>
+          <t>38254</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,66%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71566</t>
+          <t>71502</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85337</t>
+          <t>85877</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>62046</t>
+          <t>61858</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>74639</t>
+          <t>75491</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,95%</t>
+          <t>75,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138524</t>
+          <t>138376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>157212</t>
+          <t>157696</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>78,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,28%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11338</t>
+          <t>11354</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28320</t>
+          <t>28276</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>25,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8944</t>
+          <t>8938</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23448</t>
+          <t>23229</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,57%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23878</t>
+          <t>23921</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46002</t>
+          <t>46588</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,33%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>82149</t>
+          <t>82193</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>99131</t>
+          <t>99115</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,36%</t>
+          <t>74,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>95273</t>
+          <t>95492</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>109777</t>
+          <t>109783</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,25%</t>
+          <t>80,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>183189</t>
+          <t>182603</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>205313</t>
+          <t>205270</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,93%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,56%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21413</t>
+          <t>22024</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41713</t>
+          <t>42462</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>13610</t>
+          <t>14067</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>31994</t>
+          <t>32833</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>41144</t>
+          <t>40655</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>69552</t>
+          <t>67754</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178848</t>
+          <t>178099</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>199148</t>
+          <t>198537</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>213499</t>
+          <t>212660</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>231883</t>
+          <t>231426</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>396502</t>
+          <t>398300</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>424910</t>
+          <t>425399</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,28%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22325</t>
+          <t>22469</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44253</t>
+          <t>44573</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>14548</t>
+          <t>15562</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>35098</t>
+          <t>34185</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,34%</t>
+          <t>11,05%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>42495</t>
+          <t>41148</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71330</t>
+          <t>71597</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,73%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>256839</t>
+          <t>256519</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>278767</t>
+          <t>278623</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,3%</t>
+          <t>85,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,59%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>274344</t>
+          <t>275257</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>294894</t>
+          <t>293880</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,66%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>94,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>539204</t>
+          <t>538937</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>568039</t>
+          <t>569386</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,27%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,26%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>151556</t>
+          <t>152374</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>204574</t>
+          <t>203455</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,76%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,79%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>118904</t>
+          <t>118514</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>164076</t>
+          <t>167653</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>281649</t>
+          <t>284463</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>352236</t>
+          <t>353780</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,19%</t>
+          <t>13,25%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1083678</t>
+          <t>1084797</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1136696</t>
+          <t>1135878</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>84,21%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,24%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1218187</t>
+          <t>1214610</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1263359</t>
+          <t>1263749</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>87,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2318279</t>
+          <t>2316735</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2388866</t>
+          <t>2386052</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,81%</t>
+          <t>86,75%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>89,45%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2012</t>
+          <t>Población según si viven actualmente en pareja en 2012 (tasa de respuesta: 97,56%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>19823</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38411</t>
+          <t>39506</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,59%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>16753</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36849</t>
+          <t>36060</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,84%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41830</t>
+          <t>40397</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68528</t>
+          <t>68042</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,28%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,12%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>91403</t>
+          <t>90308</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>111636</t>
+          <t>109991</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,41%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>75343</t>
+          <t>76132</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95627</t>
+          <t>95439</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,16%</t>
+          <t>67,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>85,07%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173479</t>
+          <t>173965</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>200177</t>
+          <t>201610</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>82,72%</t>
+          <t>83,31%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20157</t>
+          <t>20225</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40769</t>
+          <t>41322</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17686</t>
+          <t>17005</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37070</t>
+          <t>37556</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>18,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43319</t>
+          <t>43360</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>73201</t>
+          <t>72888</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>151231</t>
+          <t>150678</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>171843</t>
+          <t>171775</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,77%</t>
+          <t>78,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,5%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160741</t>
+          <t>160255</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>180125</t>
+          <t>180806</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,26%</t>
+          <t>81,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>316610</t>
+          <t>316923</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>346492</t>
+          <t>346451</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,89%</t>
+          <t>88,88%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9367</t>
+          <t>8622</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23190</t>
+          <t>23613</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6740</t>
+          <t>6507</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22988</t>
+          <t>24739</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19856</t>
+          <t>19038</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>41937</t>
+          <t>38729</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>13,9%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>115112</t>
+          <t>114689</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>128935</t>
+          <t>129680</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>83,23%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>117290</t>
+          <t>115539</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133538</t>
+          <t>133771</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>82,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,2%</t>
+          <t>95,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>236643</t>
+          <t>239851</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>258724</t>
+          <t>259542</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,17%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>24022</t>
+          <t>23578</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46809</t>
+          <t>46230</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18794</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38302</t>
+          <t>38000</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,28%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46265</t>
+          <t>45790</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75601</t>
+          <t>77423</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>25,36%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107858</t>
+          <t>108437</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130645</t>
+          <t>131089</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,74%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112332</t>
+          <t>112634</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131840</t>
+          <t>132130</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,72%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>229700</t>
+          <t>227878</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>259036</t>
+          <t>259511</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,24%</t>
+          <t>74,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,0%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4511</t>
+          <t>4982</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18298</t>
+          <t>18100</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,59%</t>
+          <t>21,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8489</t>
+          <t>8573</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23459</t>
+          <t>23232</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16831</t>
+          <t>16289</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36656</t>
+          <t>35950</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,36%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66457</t>
+          <t>66655</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>80244</t>
+          <t>79773</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>94,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68357</t>
+          <t>68584</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>83327</t>
+          <t>83243</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,45%</t>
+          <t>74,7%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>139915</t>
+          <t>140621</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>159740</t>
+          <t>160282</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>79,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,47%</t>
+          <t>90,77%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5171</t>
+          <t>5923</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>20754</t>
+          <t>22461</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2407</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13207</t>
+          <t>12144</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10444</t>
+          <t>10734</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28407</t>
+          <t>28517</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,64%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>83121</t>
+          <t>81414</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>98704</t>
+          <t>97952</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>92046</t>
+          <t>93109</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>102358</t>
+          <t>102846</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,45%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,25%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>180721</t>
+          <t>180611</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>198684</t>
+          <t>198394</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,01%</t>
+          <t>94,87%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>34209</t>
+          <t>32134</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>60078</t>
+          <t>59688</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>40225</t>
+          <t>38690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>67561</t>
+          <t>66167</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>79751</t>
+          <t>78331</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>116802</t>
+          <t>118385</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>21,3%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>207437</t>
+          <t>207827</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>233306</t>
+          <t>235381</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>220844</t>
+          <t>222238</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>248180</t>
+          <t>249715</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>439118</t>
+          <t>437535</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>476169</t>
+          <t>477589</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,91%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26254</t>
+          <t>25478</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51877</t>
+          <t>51264</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,61%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26947</t>
+          <t>26282</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51989</t>
+          <t>51127</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,79%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>57872</t>
+          <t>58910</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>95032</t>
+          <t>91708</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,62%</t>
+          <t>14,11%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>260535</t>
+          <t>261148</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>286158</t>
+          <t>286934</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,39%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>285405</t>
+          <t>286267</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>310447</t>
+          <t>311112</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,85%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>554774</t>
+          <t>558098</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>591934</t>
+          <t>590896</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,38%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>187924</t>
+          <t>185313</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>245821</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>177179</t>
+          <t>176522</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>229468</t>
+          <t>230592</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,12%</t>
+          <t>16,2%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>374364</t>
+          <t>375886</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>452819</t>
+          <t>456788</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,34%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1137519</t>
+          <t>1141846</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1195416</t>
+          <t>1198027</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1194315</t>
+          <t>1193191</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1246604</t>
+          <t>1247261</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2354304</t>
+          <t>2350335</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2432759</t>
+          <t>2431237</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>86,61%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2016</t>
+          <t>Población según si viven actualmente en pareja en 2016 (tasa de respuesta: 97,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18908</t>
+          <t>19412</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>39642</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,49%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27209</t>
+          <t>27268</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>48812</t>
+          <t>49671</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,28%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,59%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>50814</t>
+          <t>52686</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>80539</t>
+          <t>81942</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>19,78%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,76%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86839</t>
+          <t>85638</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106372</t>
+          <t>105868</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,32%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92294</t>
+          <t>91435</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113897</t>
+          <t>113838</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>185847</t>
+          <t>184444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>215572</t>
+          <t>213700</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,24%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,22%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14146</t>
+          <t>13871</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33836</t>
+          <t>33014</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9847</t>
+          <t>9810</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26276</t>
+          <t>25037</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27719</t>
+          <t>27875</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>53561</t>
+          <t>52357</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>169441</t>
+          <t>170263</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>189131</t>
+          <t>189406</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,04%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>179555</t>
+          <t>180794</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>195984</t>
+          <t>196021</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,23%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>355547</t>
+          <t>356751</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>381389</t>
+          <t>381233</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,91%</t>
+          <t>87,2%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,22%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9951</t>
+          <t>10631</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24587</t>
+          <t>26137</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7878</t>
+          <t>7683</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22557</t>
+          <t>22199</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20981</t>
+          <t>20819</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>40829</t>
+          <t>42671</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>16,24%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>89151</t>
+          <t>87601</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103787</t>
+          <t>103107</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>77,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>91,25%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126377</t>
+          <t>126735</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141056</t>
+          <t>141251</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>221843</t>
+          <t>220001</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>241691</t>
+          <t>241853</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46432</t>
+          <t>45080</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71245</t>
+          <t>71425</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>43,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35663</t>
+          <t>35600</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59774</t>
+          <t>59101</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,09%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,67%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89787</t>
+          <t>89109</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124115</t>
+          <t>125179</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,16%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,47%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94437</t>
+          <t>94257</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119250</t>
+          <t>120602</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>117770</t>
+          <t>118443</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>141881</t>
+          <t>141944</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,33%</t>
+          <t>66,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,91%</t>
+          <t>79,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>219111</t>
+          <t>218047</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>253439</t>
+          <t>254117</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,84%</t>
+          <t>74,04%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4199</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16284</t>
+          <t>16271</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,05%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1986</t>
+          <t>2586</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10815</t>
+          <t>11233</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>8733</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23177</t>
+          <t>23484</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69201</t>
+          <t>69214</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81286</t>
+          <t>81723</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>59381</t>
+          <t>58963</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68210</t>
+          <t>67610</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,0%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>132504</t>
+          <t>132197</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146994</t>
+          <t>146948</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,39%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3657</t>
+          <t>2970</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14352</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2799</t>
+          <t>2870</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13022</t>
+          <t>13167</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8478</t>
+          <t>8456</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22958</t>
+          <t>22361</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,4%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90179</t>
+          <t>90689</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>100874</t>
+          <t>101561</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>86,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>97353</t>
+          <t>97208</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>107576</t>
+          <t>107505</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,2%</t>
+          <t>88,07%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>191948</t>
+          <t>192545</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>206428</t>
+          <t>206450</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,07%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44711</t>
+          <t>44191</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72692</t>
+          <t>72958</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35369</t>
+          <t>34977</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>63298</t>
+          <t>60960</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>16,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88015</t>
+          <t>87369</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>126567</t>
+          <t>126113</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,48%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,02%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>247680</t>
+          <t>247414</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>275661</t>
+          <t>276181</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,04%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>316216</t>
+          <t>318554</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>344145</t>
+          <t>344537</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,32%</t>
+          <t>83,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>573319</t>
+          <t>573773</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>611871</t>
+          <t>612517</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>87,52%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41700</t>
+          <t>40706</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>68374</t>
+          <t>69342</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>38810</t>
+          <t>37871</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63758</t>
+          <t>63917</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>86506</t>
+          <t>87483</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>126860</t>
+          <t>125987</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>18,04%</t>
+          <t>17,92%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>275204</t>
+          <t>274236</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>301878</t>
+          <t>302872</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>295858</t>
+          <t>295699</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>320806</t>
+          <t>321745</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>576333</t>
+          <t>577206</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>616687</t>
+          <t>615710</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>81,96%</t>
+          <t>82,08%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,56%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>227296</t>
+          <t>227067</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>286069</t>
+          <t>287809</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>19,69%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>197988</t>
+          <t>197057</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>253637</t>
+          <t>255272</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>438777</t>
+          <t>441393</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>521238</t>
+          <t>522749</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1175873</t>
+          <t>1174133</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1234646</t>
+          <t>1234875</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>80,31%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1339478</t>
+          <t>1337843</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1395127</t>
+          <t>1396058</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,98%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2533820</t>
+          <t>2532309</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2616281</t>
+          <t>2613665</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,55%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si viven actualmente en pareja en 2023</t>
+          <t>Población según si viven actualmente en pareja en 2023 (tasa de respuesta: 99,67%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18854</t>
+          <t>18124</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43066</t>
+          <t>43868</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16431</t>
+          <t>16203</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35415</t>
+          <t>35917</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,31%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40994</t>
+          <t>40775</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70019</t>
+          <t>69557</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,36%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>121210</t>
+          <t>120408</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>145422</t>
+          <t>146152</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,78%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98045</t>
+          <t>97543</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117029</t>
+          <t>117257</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,46%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>227717</t>
+          <t>228179</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256742</t>
+          <t>256961</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,48%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,3%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36126</t>
+          <t>33855</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70774</t>
+          <t>70555</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,1%</t>
+          <t>25,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38464</t>
+          <t>38920</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64002</t>
+          <t>64278</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80346</t>
+          <t>79593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>127333</t>
+          <t>124066</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,05%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,23%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>211175</t>
+          <t>211394</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>245823</t>
+          <t>248094</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,9%</t>
+          <t>74,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>188021</t>
+          <t>187745</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>213559</t>
+          <t>213103</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,6%</t>
+          <t>74,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,74%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>406639</t>
+          <t>409906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>453626</t>
+          <t>454379</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>84,95%</t>
+          <t>85,09%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11862</t>
+          <t>11856</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28482</t>
+          <t>28350</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,55%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>17844</t>
+          <t>18415</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>34511</t>
+          <t>35406</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,36%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>34760</t>
+          <t>33681</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>58660</t>
+          <t>57770</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,37%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133839</t>
+          <t>133971</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150459</t>
+          <t>150465</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,45%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>156073</t>
+          <t>155178</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>172740</t>
+          <t>172169</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,64%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>294246</t>
+          <t>295136</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>318146</t>
+          <t>319225</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,46%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30343</t>
+          <t>31025</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>62630</t>
+          <t>63112</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>17,8%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,94%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>13819</t>
+          <t>15880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52563</t>
+          <t>53756</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45869</t>
+          <t>47213</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106925</t>
+          <t>106700</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>24,06%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111645</t>
+          <t>111163</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143932</t>
+          <t>143250</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,79%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>82,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>216585</t>
+          <t>215392</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>255329</t>
+          <t>253268</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,47%</t>
+          <t>80,03%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>336498</t>
+          <t>336723</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>397554</t>
+          <t>396210</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,35%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3776</t>
+          <t>3866</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14685</t>
+          <t>14836</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,99%</t>
+          <t>17,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5431</t>
+          <t>6056</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14702</t>
+          <t>14938</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12045</t>
+          <t>11904</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26119</t>
+          <t>26349</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>14,89%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71740</t>
+          <t>71589</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82649</t>
+          <t>82559</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75866</t>
+          <t>75630</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>85137</t>
+          <t>84512</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,77%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>150874</t>
+          <t>150644</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>164948</t>
+          <t>165089</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,27%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10766</t>
+          <t>10390</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25704</t>
+          <t>25233</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>17,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11041</t>
+          <t>11668</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26050</t>
+          <t>26745</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25804</t>
+          <t>25799</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>47230</t>
+          <t>46328</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12507,7 +12507,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>16,75%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>115834</t>
+          <t>116305</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>130772</t>
+          <t>131148</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>81,84%</t>
+          <t>82,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>109021</t>
+          <t>108326</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>124030</t>
+          <t>123403</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,2%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,83%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>229379</t>
+          <t>230281</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>250805</t>
+          <t>250810</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>83,25%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>35976</t>
+          <t>36504</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68238</t>
+          <t>68318</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,78%</t>
+          <t>21,8%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39382</t>
+          <t>39398</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64517</t>
+          <t>64871</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>83196</t>
+          <t>82611</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>125820</t>
+          <t>123167</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>245124</t>
+          <t>245044</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>277386</t>
+          <t>276858</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,22%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>88,35%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>261419</t>
+          <t>261065</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>286554</t>
+          <t>286538</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,21%</t>
+          <t>80,1%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>513478</t>
+          <t>516131</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>556102</t>
+          <t>556687</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>87,08%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>27496</t>
+          <t>26680</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>52904</t>
+          <t>52426</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>17,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>8917</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>23491</t>
+          <t>22985</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>38261</t>
+          <t>39525</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>68725</t>
+          <t>68189</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>252538</t>
+          <t>253016</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>277946</t>
+          <t>278762</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>91,27%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>331908</t>
+          <t>332414</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>346988</t>
+          <t>346482</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>93,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>592116</t>
+          <t>592652</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>622580</t>
+          <t>621316</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>224744</t>
+          <t>223772</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>295040</t>
+          <t>297705</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>193613</t>
+          <t>195437</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>261573</t>
+          <t>260487</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>440373</t>
+          <t>439869</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>543579</t>
+          <t>536616</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,87%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1334548</t>
+          <t>1331883</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1404844</t>
+          <t>1405816</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1490616</t>
+          <t>1491702</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1558576</t>
+          <t>1556752</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2838198</t>
+          <t>2845161</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2941404</t>
+          <t>2941908</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,99%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P59A-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P59A-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10308</t>
+          <t>10608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>26901</t>
+          <t>26112</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>23,4%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7260</t>
+          <t>7153</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>22860</t>
+          <t>21940</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>21939</t>
+          <t>21378</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>44199</t>
+          <t>41981</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88046</t>
+          <t>88835</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>104639</t>
+          <t>104339</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>76,6%</t>
+          <t>77,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,77%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97200</t>
+          <t>98120</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>112800</t>
+          <t>112907</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,95%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>190808</t>
+          <t>193026</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>213068</t>
+          <t>213629</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>82,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,9%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13469</t>
+          <t>13076</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33646</t>
+          <t>32299</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12046</t>
+          <t>11951</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>29851</t>
+          <t>29457</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>15,17%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>29408</t>
+          <t>29238</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>56769</t>
+          <t>57366</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,91%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154329</t>
+          <t>155676</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>174506</t>
+          <t>174899</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>92,83%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>166968</t>
+          <t>167362</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184773</t>
+          <t>184868</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>84,83%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>328026</t>
+          <t>327429</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>355387</t>
+          <t>355557</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,4%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>11752</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28075</t>
+          <t>27814</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>10,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7074</t>
+          <t>6913</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20277</t>
+          <t>20181</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>21213</t>
+          <t>21274</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42315</t>
+          <t>42080</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,54%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87947</t>
+          <t>88208</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104507</t>
+          <t>104270</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,08%</t>
+          <t>89,87%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>118040</t>
+          <t>118136</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>131243</t>
+          <t>131404</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>85,41%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>212024</t>
+          <t>212259</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>233126</t>
+          <t>233065</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,36%</t>
+          <t>83,46%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,64%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14176</t>
+          <t>14698</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>31667</t>
+          <t>32114</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15366</t>
+          <t>14862</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>32476</t>
+          <t>33520</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>33066</t>
+          <t>32809</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>58305</t>
+          <t>57880</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,44%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>110585</t>
+          <t>110138</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128076</t>
+          <t>127554</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>89,67%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>139238</t>
+          <t>138194</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>156348</t>
+          <t>156852</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>81,09%</t>
+          <t>80,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>255661</t>
+          <t>256086</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>280900</t>
+          <t>281157</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>81,43%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,55%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>23432</t>
+          <t>23905</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>6473</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19838</t>
+          <t>20941</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>24,28%</t>
+          <t>25,63%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18934</t>
+          <t>18521</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38254</t>
+          <t>38431</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,49%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71502</t>
+          <t>71029</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>85877</t>
+          <t>85417</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,32%</t>
+          <t>74,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>89,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>61858</t>
+          <t>60755</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>75491</t>
+          <t>75223</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>75,72%</t>
+          <t>74,37%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>138376</t>
+          <t>138199</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>157696</t>
+          <t>158109</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,51%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11354</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28276</t>
+          <t>28116</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8938</t>
+          <t>9260</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>23229</t>
+          <t>24281</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,57%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23921</t>
+          <t>24496</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46588</t>
+          <t>46078</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,1%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>82193</t>
+          <t>82353</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>99115</t>
+          <t>99083</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>74,4%</t>
+          <t>74,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>95492</t>
+          <t>94440</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>109783</t>
+          <t>109461</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,43%</t>
+          <t>79,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>182603</t>
+          <t>183113</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>205270</t>
+          <t>204695</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,31%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22024</t>
+          <t>22080</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>42462</t>
+          <t>43255</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>19,61%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14067</t>
+          <t>13331</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>32833</t>
+          <t>31269</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>40655</t>
+          <t>40642</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>67754</t>
+          <t>66665</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>178099</t>
+          <t>177306</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>198537</t>
+          <t>198481</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>80,75%</t>
+          <t>80,39%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>90,01%</t>
+          <t>89,99%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>212660</t>
+          <t>214224</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>231426</t>
+          <t>232162</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,63%</t>
+          <t>87,26%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>398300</t>
+          <t>399389</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>425399</t>
+          <t>425412</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>85,46%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22469</t>
+          <t>22904</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44573</t>
+          <t>45542</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>15562</t>
+          <t>14478</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>34185</t>
+          <t>34600</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>41148</t>
+          <t>41591</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>71597</t>
+          <t>69575</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,4%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>256519</t>
+          <t>255550</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>278623</t>
+          <t>278188</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>85,2%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>92,39%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>275257</t>
+          <t>274842</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>293880</t>
+          <t>294964</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>538937</t>
+          <t>540959</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>569386</t>
+          <t>568943</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,27%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>93,19%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>152374</t>
+          <t>152328</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>203455</t>
+          <t>203813</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>118514</t>
+          <t>119166</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>167653</t>
+          <t>166694</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>284463</t>
+          <t>284529</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>353780</t>
+          <t>357341</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>13,25%</t>
+          <t>13,38%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1084797</t>
+          <t>1084439</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1135878</t>
+          <t>1135924</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>84,21%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1214610</t>
+          <t>1215569</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1263749</t>
+          <t>1263097</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>87,87%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,43%</t>
+          <t>91,38%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2316735</t>
+          <t>2313174</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2386052</t>
+          <t>2385986</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>86,75%</t>
+          <t>86,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19823</t>
+          <t>20036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39506</t>
+          <t>39383</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16753</t>
+          <t>16359</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36060</t>
+          <t>36153</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40397</t>
+          <t>42214</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>68042</t>
+          <t>69404</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,68%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90308</t>
+          <t>90431</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>109991</t>
+          <t>109778</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,57%</t>
+          <t>69,66%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>76132</t>
+          <t>76039</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95439</t>
+          <t>95833</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,78%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>173965</t>
+          <t>172603</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>201610</t>
+          <t>199793</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>82,56%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>20225</t>
+          <t>20064</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41322</t>
+          <t>40033</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17005</t>
+          <t>18054</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>37556</t>
+          <t>37969</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>43360</t>
+          <t>44777</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72888</t>
+          <t>73306</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>18,81%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>150678</t>
+          <t>151967</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>171775</t>
+          <t>171936</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,48%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>160255</t>
+          <t>159842</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>180806</t>
+          <t>179757</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>90,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>316923</t>
+          <t>316505</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>346451</t>
+          <t>345034</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>81,3%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>8622</t>
+          <t>8814</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23613</t>
+          <t>24070</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6507</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>24739</t>
+          <t>22937</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>17,64%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>19038</t>
+          <t>18913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>38729</t>
+          <t>40803</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>114689</t>
+          <t>114232</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>129680</t>
+          <t>129488</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,93%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>93,77%</t>
+          <t>93,63%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115539</t>
+          <t>117341</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>133771</t>
+          <t>133644</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>82,36%</t>
+          <t>83,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>239851</t>
+          <t>237777</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>259542</t>
+          <t>259667</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>85,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,17%</t>
+          <t>93,21%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23578</t>
+          <t>24294</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>46230</t>
+          <t>46974</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>30,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>18504</t>
+          <t>18374</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38000</t>
+          <t>37587</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45790</t>
+          <t>47046</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>77423</t>
+          <t>75571</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>24,75%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>108437</t>
+          <t>107693</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131089</t>
+          <t>130373</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,29%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112634</t>
+          <t>113047</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>132130</t>
+          <t>132260</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>74,77%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,72%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>227878</t>
+          <t>229730</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>259511</t>
+          <t>258255</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,64%</t>
+          <t>75,25%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,59%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4982</t>
+          <t>4449</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18100</t>
+          <t>18892</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>22,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8573</t>
+          <t>8971</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>23232</t>
+          <t>22651</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16289</t>
+          <t>16595</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35950</t>
+          <t>36066</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,43%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>66655</t>
+          <t>65863</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>79773</t>
+          <t>80306</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>77,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>68584</t>
+          <t>69165</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>83243</t>
+          <t>82845</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>140621</t>
+          <t>140505</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>160282</t>
+          <t>159976</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>79,64%</t>
+          <t>79,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,6%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>5923</t>
+          <t>5950</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22461</t>
+          <t>22027</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2407</t>
+          <t>2175</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12144</t>
+          <t>12090</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>10734</t>
+          <t>10523</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>28517</t>
+          <t>29028</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,88%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>81414</t>
+          <t>81848</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>97952</t>
+          <t>97925</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>93109</t>
+          <t>93163</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>102846</t>
+          <t>103078</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,51%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>180611</t>
+          <t>180100</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>198394</t>
+          <t>198605</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,97%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>32134</t>
+          <t>34342</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59688</t>
+          <t>58803</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>12,84%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,31%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38690</t>
+          <t>39136</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66167</t>
+          <t>66690</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>78331</t>
+          <t>79524</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>118385</t>
+          <t>117313</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,1%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>207827</t>
+          <t>208712</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>235381</t>
+          <t>233173</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,69%</t>
+          <t>78,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>87,16%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>222238</t>
+          <t>221715</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>249715</t>
+          <t>249269</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>76,88%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>86,58%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>437535</t>
+          <t>438607</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>477589</t>
+          <t>476396</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,9%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,7%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>25478</t>
+          <t>25464</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>51264</t>
+          <t>49349</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>26282</t>
+          <t>26176</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>51127</t>
+          <t>51007</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>58910</t>
+          <t>56848</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>91708</t>
+          <t>92064</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>14,17%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>261148</t>
+          <t>263063</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>286934</t>
+          <t>286948</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>84,2%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,84%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>286267</t>
+          <t>286387</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>311112</t>
+          <t>311218</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>84,85%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,21%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>558098</t>
+          <t>557742</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>590896</t>
+          <t>592958</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,93%</t>
+          <t>91,25%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>185313</t>
+          <t>184121</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>241494</t>
+          <t>238355</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>176522</t>
+          <t>174290</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>230592</t>
+          <t>233501</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>375886</t>
+          <t>373746</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>456788</t>
+          <t>452634</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,12%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1141846</t>
+          <t>1144985</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1198027</t>
+          <t>1199219</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1193191</t>
+          <t>1190282</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1247261</t>
+          <t>1249493</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>83,6%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2350335</t>
+          <t>2354489</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2431237</t>
+          <t>2433377</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>86,69%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19412</t>
+          <t>18832</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39642</t>
+          <t>38990</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>27268</t>
+          <t>27515</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49671</t>
+          <t>48674</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>34,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>52686</t>
+          <t>51434</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>81942</t>
+          <t>81050</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>19,78%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,43%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>85638</t>
+          <t>86290</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>105868</t>
+          <t>106448</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91435</t>
+          <t>92432</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113838</t>
+          <t>113591</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>64,8%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>184444</t>
+          <t>185336</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>213700</t>
+          <t>214952</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>80,22%</t>
+          <t>80,69%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13871</t>
+          <t>13574</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>33014</t>
+          <t>33553</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9810</t>
+          <t>10064</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25037</t>
+          <t>25217</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>27875</t>
+          <t>28639</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>52357</t>
+          <t>54251</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,26%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>170263</t>
+          <t>169724</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>189406</t>
+          <t>189703</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>93,18%</t>
+          <t>93,32%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>180794</t>
+          <t>180614</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>196021</t>
+          <t>195767</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,84%</t>
+          <t>87,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>356751</t>
+          <t>354857</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>381233</t>
+          <t>380469</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,2%</t>
+          <t>86,74%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>93,19%</t>
+          <t>93,0%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10631</t>
+          <t>10245</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26137</t>
+          <t>25375</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>22,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7683</t>
+          <t>7740</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>22199</t>
+          <t>22006</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>20819</t>
+          <t>20540</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>42671</t>
+          <t>42248</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,08%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>87601</t>
+          <t>88363</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103107</t>
+          <t>103493</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>77,02%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>126735</t>
+          <t>126928</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141251</t>
+          <t>141194</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>85,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>220001</t>
+          <t>220424</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>241853</t>
+          <t>242132</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,18%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45080</t>
+          <t>46692</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71425</t>
+          <t>71613</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>27,21%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>43,11%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>35600</t>
+          <t>36159</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59101</t>
+          <t>59920</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,29%</t>
+          <t>33,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>89109</t>
+          <t>88942</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125179</t>
+          <t>126291</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>25,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,47%</t>
+          <t>36,8%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>94257</t>
+          <t>94069</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>120602</t>
+          <t>118990</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>56,89%</t>
+          <t>56,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>72,79%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>118443</t>
+          <t>117624</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>141944</t>
+          <t>141385</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,95%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218047</t>
+          <t>216935</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>254117</t>
+          <t>254284</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,53%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,04%</t>
+          <t>74,09%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3762</t>
+          <t>4055</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16271</t>
+          <t>16503</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2586</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>10731</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8733</t>
+          <t>8476</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>23484</t>
+          <t>23832</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,31%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>69214</t>
+          <t>68982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>81723</t>
+          <t>81430</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>80,97%</t>
+          <t>80,69%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>58963</t>
+          <t>59465</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67610</t>
+          <t>68249</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>97,23%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>132197</t>
+          <t>131849</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146948</t>
+          <t>147205</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,56%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>2970</t>
+          <t>3767</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>14408</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2870</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>13167</t>
+          <t>12048</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>10,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8456</t>
+          <t>7793</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22361</t>
+          <t>22481</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>10,46%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>90689</t>
+          <t>90123</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101561</t>
+          <t>100764</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>97,16%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>97208</t>
+          <t>98327</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>107505</t>
+          <t>107646</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>192545</t>
+          <t>192425</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>206450</t>
+          <t>207113</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,54%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,37%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>44191</t>
+          <t>44696</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72958</t>
+          <t>74830</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>34977</t>
+          <t>35803</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>60960</t>
+          <t>61515</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,06%</t>
+          <t>16,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>87369</t>
+          <t>87619</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>126113</t>
+          <t>126192</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,03%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>247414</t>
+          <t>245542</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>276181</t>
+          <t>275676</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>76,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>318554</t>
+          <t>317999</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>344537</t>
+          <t>343711</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>83,94%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>573773</t>
+          <t>573694</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>612517</t>
+          <t>612267</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,97%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,48%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>40706</t>
+          <t>41284</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>69342</t>
+          <t>69041</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,85%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>37871</t>
+          <t>37671</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>63917</t>
+          <t>62749</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>87483</t>
+          <t>86460</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>125987</t>
+          <t>124415</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,92%</t>
+          <t>17,69%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>274236</t>
+          <t>274537</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>302872</t>
+          <t>302294</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>79,82%</t>
+          <t>79,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>88,15%</t>
+          <t>87,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>295699</t>
+          <t>296867</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>321745</t>
+          <t>321945</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>577206</t>
+          <t>578778</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>615710</t>
+          <t>616733</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>82,08%</t>
+          <t>82,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,7%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>227067</t>
+          <t>226086</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>287809</t>
+          <t>284564</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,46%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>197057</t>
+          <t>196240</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>255272</t>
+          <t>254437</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>441393</t>
+          <t>439242</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>522749</t>
+          <t>521488</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,07%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1174133</t>
+          <t>1177378</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1234875</t>
+          <t>1235856</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,54%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1337843</t>
+          <t>1338678</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1396058</t>
+          <t>1396875</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>83,98%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2532309</t>
+          <t>2533570</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2613665</t>
+          <t>2615816</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>85,55%</t>
+          <t>85,62%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>29487</t>
+          <t>27478</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18124</t>
+          <t>19168</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43868</t>
+          <t>38982</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>25,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>24522</t>
+          <t>25995</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16203</t>
+          <t>18573</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>35917</t>
+          <t>35889</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>12,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>54009</t>
+          <t>53473</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40775</t>
+          <t>41214</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>69557</t>
+          <t>67432</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>23,36%</t>
+          <t>22,53%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>134789</t>
+          <t>124547</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>120408</t>
+          <t>113043</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146152</t>
+          <t>132857</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>74,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>108938</t>
+          <t>121261</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>97543</t>
+          <t>111367</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>117257</t>
+          <t>128683</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>81,63%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>243727</t>
+          <t>245808</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>228179</t>
+          <t>231849</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>256961</t>
+          <t>258067</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>76,64%</t>
+          <t>77,47%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,23%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>164276</t>
+          <t>152025</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>164276</t>
+          <t>152025</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>164276</t>
+          <t>152025</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>133460</t>
+          <t>147256</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>133460</t>
+          <t>147256</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>133460</t>
+          <t>147256</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>297736</t>
+          <t>299281</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>297736</t>
+          <t>299281</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>297736</t>
+          <t>299281</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50811</t>
+          <t>52248</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33855</t>
+          <t>37856</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>70555</t>
+          <t>72609</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>25,02%</t>
+          <t>26,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49895</t>
+          <t>51823</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>38920</t>
+          <t>39626</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64278</t>
+          <t>65165</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>25,5%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>100706</t>
+          <t>104071</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>79593</t>
+          <t>81860</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124066</t>
+          <t>127398</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>18,86%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,91%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>231138</t>
+          <t>223932</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>211394</t>
+          <t>203571</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>248094</t>
+          <t>238324</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,08%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>73,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>202128</t>
+          <t>213391</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>187745</t>
+          <t>200049</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>213103</t>
+          <t>225588</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,46%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>74,5%</t>
+          <t>75,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>433266</t>
+          <t>437322</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>409906</t>
+          <t>413995</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>454379</t>
+          <t>459533</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>80,78%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,47%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>85,09%</t>
+          <t>84,88%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>281949</t>
+          <t>276180</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>281949</t>
+          <t>276180</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>281949</t>
+          <t>276180</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>252023</t>
+          <t>265214</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>252023</t>
+          <t>265214</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>252023</t>
+          <t>265214</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>533972</t>
+          <t>541393</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>533972</t>
+          <t>541393</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>533972</t>
+          <t>541393</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>19027</t>
+          <t>21623</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11856</t>
+          <t>14423</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28350</t>
+          <t>32462</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>7,3%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>25690</t>
+          <t>25962</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>18415</t>
+          <t>18485</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>35406</t>
+          <t>35418</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>18,48%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>44716</t>
+          <t>47584</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33681</t>
+          <t>36676</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>57770</t>
+          <t>61581</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,37%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>143294</t>
+          <t>141038</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>133971</t>
+          <t>130199</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>150465</t>
+          <t>148238</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>82,53%</t>
+          <t>80,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>92,7%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>164894</t>
+          <t>165716</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>155178</t>
+          <t>156260</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>172169</t>
+          <t>173193</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>86,52%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>81,42%</t>
+          <t>81,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>308190</t>
+          <t>306754</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>295136</t>
+          <t>292757</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>319225</t>
+          <t>317662</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>86,57%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>83,63%</t>
+          <t>82,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>89,65%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>162321</t>
+          <t>162661</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>162321</t>
+          <t>162661</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>162321</t>
+          <t>162661</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>190584</t>
+          <t>191678</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>190584</t>
+          <t>191678</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>190584</t>
+          <t>191678</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>352906</t>
+          <t>354338</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>352906</t>
+          <t>354338</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>352906</t>
+          <t>354338</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45405</t>
+          <t>52202</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31025</t>
+          <t>34528</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>63112</t>
+          <t>70851</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>34666</t>
+          <t>39399</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15880</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>53756</t>
+          <t>53794</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>23,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>80071</t>
+          <t>91602</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>47213</t>
+          <t>70675</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>106700</t>
+          <t>119102</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>21,12%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>128870</t>
+          <t>155891</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>111163</t>
+          <t>137242</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>143250</t>
+          <t>173565</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>73,95%</t>
+          <t>74,91%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,79%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>234482</t>
+          <t>186134</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>215392</t>
+          <t>171739</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>253268</t>
+          <t>196860</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>363352</t>
+          <t>342024</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>336723</t>
+          <t>314524</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>396210</t>
+          <t>362951</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>78,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,94%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>83,7%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>174275</t>
+          <t>208093</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>174275</t>
+          <t>208093</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>174275</t>
+          <t>208093</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>269148</t>
+          <t>225533</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>269148</t>
+          <t>225533</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>269148</t>
+          <t>225533</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>443423</t>
+          <t>433626</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>443423</t>
+          <t>433626</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>443423</t>
+          <t>433626</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>7996</t>
+          <t>8631</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3866</t>
+          <t>4352</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>14836</t>
+          <t>17005</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9646</t>
+          <t>11193</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6056</t>
+          <t>6965</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14938</t>
+          <t>16929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>16,49%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>17643</t>
+          <t>19825</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11904</t>
+          <t>13326</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26349</t>
+          <t>28678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,44%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>78429</t>
+          <t>90893</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>71589</t>
+          <t>82519</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82559</t>
+          <t>95172</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>82,83%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>80922</t>
+          <t>87869</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>75630</t>
+          <t>82133</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>84512</t>
+          <t>92097</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,35%</t>
+          <t>88,7%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>83,51%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,31%</t>
+          <t>92,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>159350</t>
+          <t>178760</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>150644</t>
+          <t>169907</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>165089</t>
+          <t>185259</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,03%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,29%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>86425</t>
+          <t>99524</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>86425</t>
+          <t>99524</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>86425</t>
+          <t>99524</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>90568</t>
+          <t>99062</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>90568</t>
+          <t>99062</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>90568</t>
+          <t>99062</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>176993</t>
+          <t>198585</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>176993</t>
+          <t>198585</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>176993</t>
+          <t>198585</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>16905</t>
+          <t>17403</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>10390</t>
+          <t>10936</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>25233</t>
+          <t>24781</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18308</t>
+          <t>18409</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>11668</t>
+          <t>12120</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26745</t>
+          <t>26896</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,4%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>35213</t>
+          <t>35812</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25799</t>
+          <t>26912</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>46328</t>
+          <t>47374</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>12,98%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,17%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>124633</t>
+          <t>121186</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>116305</t>
+          <t>113808</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>131148</t>
+          <t>127653</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>82,17%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>116763</t>
+          <t>118942</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>108326</t>
+          <t>110455</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>123403</t>
+          <t>125231</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,6%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>80,2%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>241396</t>
+          <t>240128</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>230281</t>
+          <t>228566</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>250810</t>
+          <t>249028</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>87,27%</t>
+          <t>87,02%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>82,83%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,25%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>141538</t>
+          <t>138589</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>141538</t>
+          <t>138589</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>141538</t>
+          <t>138589</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>135071</t>
+          <t>137351</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>135071</t>
+          <t>137351</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>135071</t>
+          <t>137351</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>276609</t>
+          <t>275940</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>276609</t>
+          <t>275940</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>276609</t>
+          <t>275940</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>50887</t>
+          <t>59616</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36504</t>
+          <t>43965</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68318</t>
+          <t>78282</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,8%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>51691</t>
+          <t>66747</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39398</t>
+          <t>52770</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>64871</t>
+          <t>83149</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>21,31%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>102578</t>
+          <t>126363</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82611</t>
+          <t>105619</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>123167</t>
+          <t>151407</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>17,03%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>12,92%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>19,27%</t>
+          <t>20,4%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>262475</t>
+          <t>292246</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>245044</t>
+          <t>273580</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>276858</t>
+          <t>307897</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,06%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>78,2%</t>
+          <t>77,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>274245</t>
+          <t>323470</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>261065</t>
+          <t>307068</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>286538</t>
+          <t>337447</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>82,89%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>78,69%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>536720</t>
+          <t>615716</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>516131</t>
+          <t>590672</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>556687</t>
+          <t>636460</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>82,97%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>87,08%</t>
+          <t>85,77%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>313362</t>
+          <t>351862</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>313362</t>
+          <t>351862</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>313362</t>
+          <t>351862</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>325936</t>
+          <t>390217</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>325936</t>
+          <t>390217</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>325936</t>
+          <t>390217</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>639298</t>
+          <t>742079</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>639298</t>
+          <t>742079</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>639298</t>
+          <t>742079</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>37988</t>
+          <t>45997</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>26680</t>
+          <t>32673</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>52426</t>
+          <t>61663</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,73%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>14579</t>
+          <t>18158</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>8917</t>
+          <t>10487</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>22985</t>
+          <t>28638</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,47%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>52568</t>
+          <t>64155</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>39525</t>
+          <t>48199</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>68189</t>
+          <t>83388</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>267454</t>
+          <t>314097</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>253016</t>
+          <t>298431</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>278762</t>
+          <t>327421</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>87,56%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>91,27%</t>
+          <t>90,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>340820</t>
+          <t>396778</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>332414</t>
+          <t>386298</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>346482</t>
+          <t>404449</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>93,53%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,47%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>608273</t>
+          <t>710875</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>592652</t>
+          <t>691642</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>621316</t>
+          <t>726831</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>92,05%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>93,78%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>305442</t>
+          <t>360094</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>305442</t>
+          <t>360094</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>305442</t>
+          <t>360094</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>355399</t>
+          <t>414936</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>355399</t>
+          <t>414936</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>355399</t>
+          <t>414936</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>660841</t>
+          <t>775030</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>660841</t>
+          <t>775030</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>660841</t>
+          <t>775030</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>258506</t>
+          <t>285198</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>223772</t>
+          <t>249020</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>297705</t>
+          <t>325349</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>14,24%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>228998</t>
+          <t>257687</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>195437</t>
+          <t>228445</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>260487</t>
+          <t>283176</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>13,07%</t>
+          <t>13,77%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>487504</t>
+          <t>542885</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>439869</t>
+          <t>499586</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>536616</t>
+          <t>595084</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>15,0%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,44%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1371082</t>
+          <t>1463829</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1331883</t>
+          <t>1423678</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1405816</t>
+          <t>1500007</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>84,14%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>81,73%</t>
+          <t>81,4%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,27%</t>
+          <t>85,76%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1523191</t>
+          <t>1613560</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1491702</t>
+          <t>1588071</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1556752</t>
+          <t>1642802</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>86,93%</t>
+          <t>86,23%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2894273</t>
+          <t>3077389</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2845161</t>
+          <t>3025190</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2941908</t>
+          <t>3120688</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,0%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>86,2%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1629588</t>
+          <t>1749027</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1629588</t>
+          <t>1749027</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1629588</t>
+          <t>1749027</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1752189</t>
+          <t>1871247</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1752189</t>
+          <t>1871247</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1752189</t>
+          <t>1871247</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3381777</t>
+          <t>3620274</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3381777</t>
+          <t>3620274</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3381777</t>
+          <t>3620274</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
